--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008510362272481009</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39920971</v>
+        <v>4150804</v>
       </c>
       <c r="L2" t="n">
-        <v>21745998</v>
+        <v>1753527</v>
       </c>
       <c r="M2" t="n">
-        <v>5200079</v>
+        <v>345305</v>
       </c>
       <c r="N2" t="n">
-        <v>237565</v>
+        <v>8837</v>
       </c>
       <c r="O2" t="n">
-        <v>3091445</v>
+        <v>205371</v>
       </c>
       <c r="P2" t="n">
-        <v>1183842</v>
+        <v>68710</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999743700027466</v>
+        <v>0.9999318718910217</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8573296070098877</v>
+        <v>0.7428401112556458</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7399171590805054</v>
+        <v>0.5782650709152222</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6774489283561707</v>
+        <v>0.4612763226032257</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2930535078048706</v>
+        <v>0.06590939313173294</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7227783203125</v>
+        <v>0.5009525418281555</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8277162313461304</v>
+        <v>0.6643461585044861</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002038439189791413</v>
       </c>
       <c r="C3" t="n">
-        <v>1056</v>
+        <v>354</v>
       </c>
       <c r="D3" t="n">
-        <v>39920971</v>
+        <v>4150804</v>
       </c>
       <c r="E3" t="n">
-        <v>5050797</v>
+        <v>788268</v>
       </c>
       <c r="F3" t="n">
-        <v>124115</v>
+        <v>31151</v>
       </c>
       <c r="G3" t="n">
-        <v>10912</v>
+        <v>2859</v>
       </c>
       <c r="H3" t="n">
-        <v>7397</v>
+        <v>2072</v>
       </c>
       <c r="I3" t="n">
-        <v>380</v>
+        <v>147</v>
       </c>
       <c r="J3" t="n">
-        <v>90148142</v>
+        <v>10016192</v>
       </c>
       <c r="K3" t="n">
-        <v>95207421</v>
+        <v>9917000</v>
       </c>
       <c r="L3" t="n">
-        <v>109832436</v>
+        <v>11744410</v>
       </c>
       <c r="M3" t="n">
-        <v>136079810</v>
+        <v>14986440</v>
       </c>
       <c r="N3" t="n">
-        <v>145589555</v>
+        <v>16114662</v>
       </c>
       <c r="O3" t="n">
-        <v>141192155</v>
+        <v>15613629</v>
       </c>
       <c r="P3" t="n">
-        <v>144979183</v>
+        <v>16101199</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.884859025478363</v>
+        <v>0.8342226147651672</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7373977303504944</v>
+        <v>0.5303554534912109</v>
       </c>
       <c r="T3" t="n">
-        <v>0.618269681930542</v>
+        <v>0.3673930466175079</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2955685555934906</v>
+        <v>0.09852057695388794</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6737345457077026</v>
+        <v>0.4016007781028748</v>
       </c>
       <c r="W3" t="n">
-        <v>0.680053174495697</v>
+        <v>0.3547494411468506</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03213413144859563</v>
       </c>
       <c r="C4" t="n">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>6191706</v>
+        <v>1311550</v>
       </c>
       <c r="E4" t="n">
-        <v>21745998</v>
+        <v>1753527</v>
       </c>
       <c r="F4" t="n">
-        <v>1338027</v>
+        <v>191702</v>
       </c>
       <c r="G4" t="n">
-        <v>71828</v>
+        <v>18434</v>
       </c>
       <c r="H4" t="n">
-        <v>130726</v>
+        <v>28187</v>
       </c>
       <c r="I4" t="n">
-        <v>11805</v>
+        <v>2876</v>
       </c>
       <c r="J4" t="n">
-        <v>1456</v>
+        <v>430</v>
       </c>
       <c r="K4" t="n">
-        <v>6643351</v>
+        <v>1436945</v>
       </c>
       <c r="L4" t="n">
-        <v>7643776</v>
+        <v>1278866</v>
       </c>
       <c r="M4" t="n">
-        <v>2475893</v>
+        <v>403281</v>
       </c>
       <c r="N4" t="n">
-        <v>573089</v>
+        <v>125241</v>
       </c>
       <c r="O4" t="n">
-        <v>1185724</v>
+        <v>204590</v>
       </c>
       <c r="P4" t="n">
-        <v>246409</v>
+        <v>34715</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999871850013733</v>
+        <v>0.9999659657478333</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8708767890930176</v>
+        <v>0.7858837842941284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7386552691459656</v>
+        <v>0.5532750487327576</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6465077996253967</v>
+        <v>0.409016489982605</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2943056523799896</v>
+        <v>0.07898112386465073</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6973952054977417</v>
+        <v>0.4458084106445312</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7466540932655334</v>
+        <v>0.4625207185745239</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>316306</v>
+        <v>93402</v>
       </c>
       <c r="E5" t="n">
-        <v>2142803</v>
+        <v>382822</v>
       </c>
       <c r="F5" t="n">
-        <v>5200079</v>
+        <v>345305</v>
       </c>
       <c r="G5" t="n">
-        <v>188057</v>
+        <v>34817</v>
       </c>
       <c r="H5" t="n">
-        <v>514595</v>
+        <v>74167</v>
       </c>
       <c r="I5" t="n">
-        <v>48803</v>
+        <v>9352</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5194657</v>
+        <v>824851</v>
       </c>
       <c r="L5" t="n">
-        <v>7744190</v>
+        <v>1552797</v>
       </c>
       <c r="M5" t="n">
-        <v>3210618</v>
+        <v>594574</v>
       </c>
       <c r="N5" t="n">
-        <v>566191</v>
+        <v>80860</v>
       </c>
       <c r="O5" t="n">
-        <v>1497076</v>
+        <v>306010</v>
       </c>
       <c r="P5" t="n">
-        <v>556966</v>
+        <v>124976</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999901056289673</v>
+        <v>0.9999736547470093</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9194509387016296</v>
+        <v>0.8614910244941711</v>
       </c>
       <c r="S5" t="n">
-        <v>0.895296037197113</v>
+        <v>0.8265932202339172</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9613074064254761</v>
+        <v>0.9388928413391113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.992247998714447</v>
+        <v>0.9873786568641663</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9817454814910889</v>
+        <v>0.9687316417694092</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945335984230042</v>
+        <v>0.9902207851409912</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>113785</v>
+        <v>21240</v>
       </c>
       <c r="E6" t="n">
-        <v>167540</v>
+        <v>24312</v>
       </c>
       <c r="F6" t="n">
-        <v>197618</v>
+        <v>25671</v>
       </c>
       <c r="G6" t="n">
-        <v>237565</v>
+        <v>8837</v>
       </c>
       <c r="H6" t="n">
-        <v>79715</v>
+        <v>8613</v>
       </c>
       <c r="I6" t="n">
-        <v>7462</v>
+        <v>1014</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>20794</v>
+        <v>10334</v>
       </c>
       <c r="E7" t="n">
-        <v>260968</v>
+        <v>75593</v>
       </c>
       <c r="F7" t="n">
-        <v>763482</v>
+        <v>139446</v>
       </c>
       <c r="G7" t="n">
-        <v>273796</v>
+        <v>59311</v>
       </c>
       <c r="H7" t="n">
-        <v>3091445</v>
+        <v>205371</v>
       </c>
       <c r="I7" t="n">
-        <v>177959</v>
+        <v>21326</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>760</v>
+        <v>419</v>
       </c>
       <c r="E8" t="n">
-        <v>21668</v>
+        <v>7871</v>
       </c>
       <c r="F8" t="n">
-        <v>52651</v>
+        <v>15311</v>
       </c>
       <c r="G8" t="n">
-        <v>28496</v>
+        <v>9820</v>
       </c>
       <c r="H8" t="n">
-        <v>453291</v>
+        <v>91551</v>
       </c>
       <c r="I8" t="n">
-        <v>1183842</v>
+        <v>68710</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
